--- a/data/por_departamento/La Unión/establecimientos_salud.xlsx
+++ b/data/por_departamento/La Unión/establecimientos_salud.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Establecimientos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA36"/>
+  <dimension ref="A1:AA32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,7 +834,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>overpass-way-286834891</t>
+          <t>overpass-way-393900408</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>way/286834891</t>
+          <t>way/393900408</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hospital Nacional de La Unión</t>
+          <t>Unidad de Salud Concepción de Oriente</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Concepcion De Oriente</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -877,14 +877,14 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>La Unión</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -894,17 +894,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>13.347031</t>
+          <t>13.79161702</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-87.87606047</t>
+          <t>-87.71502532</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>POLYGON ((-87.8772038 13.3465709, -87.8753272 13.3460769, -87.8752685 13.3464042, -87.8750045 13.3475581, -87.8766924 13.34797, -87.876914 13.3473636, -87.8770837 13.3468996, -87.8772038 13.3465709))</t>
+          <t>POLYGON ((-87.7152337 13.7916723, -87.7151957 13.791488, -87.7148169 13.7915618, -87.7148549 13.791746, -87.7152337 13.7916723))</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/286834891</t>
+          <t>https://www.openstreetmap.org/way/393900408</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.347031,-87.87606047</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.79161702,-87.71502532</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>overpass-way-393900408</t>
+          <t>overpass-way-741010546</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -941,22 +941,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>way/393900408</t>
+          <t>way/741010546</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Unidad de Salud Concepción de Oriente</t>
+          <t>Hospital Nacional Santa Rosa de Lima</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Concepcion De Oriente</t>
+          <t>Santa Rosa de Lima</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -974,14 +974,19 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Lima</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>clinic</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>hospital</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -991,17 +996,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>13.79161702</t>
+          <t>13.62059085</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-87.71502532</t>
+          <t>-87.89683197</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1011,24 +1016,24 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>POLYGON ((-87.7152337 13.7916723, -87.7151957 13.791488, -87.7148169 13.7915618, -87.7148549 13.791746, -87.7152337 13.7916723))</t>
+          <t>POLYGON ((-87.8976044 13.6210094, -87.896947 13.6196405, -87.8960019 13.6200754, -87.8968031 13.6216039, -87.8970771 13.6214353, -87.8974537 13.6211647, -87.8976044 13.6210094))</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/393900408</t>
+          <t>https://www.openstreetmap.org/way/741010546</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.79161702,-87.71502532</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.62059085,-87.89683197</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>overpass-way-741010546</t>
+          <t>overpass-way-1121128779</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1038,22 +1043,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>way/741010546</t>
+          <t>way/1121128779</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hospital Nacional Santa Rosa de Lima</t>
+          <t>Unidad De Salud De Cantón Higueras</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1063,7 +1068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Santa Rosa de Lima</t>
+          <t>cantón Higueras</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1073,17 +1078,27 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Santa Rosa de Lima</t>
+          <t>cantón Higueras</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Medicina general</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinic</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1093,17 +1108,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>13.62059085</t>
+          <t>13.78220737</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-87.89683197</t>
+          <t>-87.92205387</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1113,24 +1128,24 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>POLYGON ((-87.8976044 13.6210094, -87.896947 13.6196405, -87.8960019 13.6200754, -87.8968031 13.6216039, -87.8970771 13.6214353, -87.8974537 13.6211647, -87.8976044 13.6210094))</t>
+          <t>POLYGON ((-87.9220588 13.7821061, -87.9219593 13.7822503, -87.922049 13.7823086, -87.9221484 13.7821645, -87.9220588 13.7821061))</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/741010546</t>
+          <t>https://www.openstreetmap.org/way/1121128779</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.62059085,-87.89683197</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.78220737,-87.92205387</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>overpass-way-1121128779</t>
+          <t>overpass-way-1221929080</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1140,12 +1155,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>way/1121128779</t>
+          <t>way/1221929080</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Unidad De Salud De Cantón Higueras</t>
+          <t>Sin nombre</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1165,7 +1180,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>cantón Higueras</t>
+          <t>San Alejo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1173,11 +1188,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>cantón Higueras</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>clinic</t>
@@ -1200,17 +1210,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>13.78220737</t>
+          <t>13.42900356</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-87.92205387</t>
+          <t>-87.96045635</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1220,49 +1230,59 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>POLYGON ((-87.9220588 13.7821061, -87.9219593 13.7822503, -87.922049 13.7823086, -87.9221484 13.7821645, -87.9220588 13.7821061))</t>
+          <t>POLYGON ((-87.9606093 13.4290643, -87.9606137 13.4289544, -87.960473 13.428949, -87.9604742 13.4289203, -87.9603319 13.4289148, -87.9603252 13.4290792, -87.9604909 13.4290856, -87.9604919 13.4290598, -87.9606093 13.4290643))</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1121128779</t>
+          <t>https://www.openstreetmap.org/way/1221929080</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.78220737,-87.92205387</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.42900356,-87.96045635</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>overpass-way-1221929080</t>
+          <t>geofabrik-way-8864711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>overpass</t>
+          <t>geofabrik</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>way/1221929080</t>
+          <t>way/8864711</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sin nombre</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Predio</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>predio</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1272,7 +1292,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>San Alejo</t>
+          <t>Yayantique</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1280,21 +1300,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>clinic</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>clinic</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>Polygon</t>
@@ -1302,17 +1307,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>13.42900356</t>
+          <t>13.44850543</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-87.96045635</t>
+          <t>-88.0229956</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1322,29 +1327,29 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>POLYGON ((-87.9606093 13.4290643, -87.9606137 13.4289544, -87.960473 13.428949, -87.9604742 13.4289203, -87.9603319 13.4289148, -87.9603252 13.4290792, -87.9604909 13.4290856, -87.9604919 13.4290598, -87.9606093 13.4290643))</t>
+          <t>POLYGON ((-88.0231178 13.4484658, -88.0231162 13.4486514, -88.0228574 13.4486394, -88.0228682 13.4484149, -88.0230793 13.4483145, -88.0231132 13.4484254, -88.0231178 13.4484658))</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1221929080</t>
+          <t>https://www.openstreetmap.org/way/8864711</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.42900356,-87.96045635</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.44850543,-88.0229956</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>geofabrik-way-286834891</t>
+          <t>hot-way-286834891</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1369,12 +1374,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>poligono</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1392,6 +1397,16 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>hospital</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>Polygon</t>
@@ -1419,7 +1434,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>POLYGON ((-87.8772038 13.3465709, -87.8770837 13.3468996, -87.876914 13.3473636, -87.8766924 13.34797, -87.8750045 13.3475581, -87.8752685 13.3464042, -87.8753272 13.3460769, -87.8772038 13.3465709))</t>
+          <t>POLYGON ((-87.8772038 13.3465709, -87.8753272 13.3460769, -87.8752685 13.3464042, -87.8750045 13.3475581, -87.8766924 13.34797, -87.876914 13.3473636, -87.8770837 13.3468996, -87.8772038 13.3465709))</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1436,42 +1451,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>geofabrik-way-8864711</t>
+          <t>hot-node-3969572342</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>way/8864711</t>
+          <t>node/3969572342</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Unidad de Salud Enfermera Ana María Alfaro de Sánchez</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1481,7 +1496,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Yayantique</t>
+          <t>Nueva Esparta</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1491,64 +1506,64 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>13.44850543</t>
+          <t>13.7842859</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-88.0229956</t>
+          <t>-87.8340675</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.0231178 13.4484658, -88.0231162 13.4486514, -88.0228574 13.4486394, -88.0228682 13.4484149, -88.0230793 13.4483145, -88.0231132 13.4484254, -88.0231178 13.4484658))</t>
+          <t>POINT (-87.8340675 13.7842859)</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/8864711</t>
+          <t>https://www.openstreetmap.org/node/3969572342</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.44850543,-88.0229956</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7842859,-87.8340675</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>geofabrik-way-1121128779</t>
+          <t>hot-node-1642100520</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>way/1121128779</t>
+          <t>node/1642100520</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Unidad De Salud De Cantón Higueras</t>
+          <t>Sin nombre</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1563,12 +1578,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1578,7 +1593,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Lislique</t>
+          <t>Polorós</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1588,49 +1603,49 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>13.78220737</t>
+          <t>13.8097739</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-87.92205387</t>
+          <t>-87.8182879</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>POLYGON ((-87.9221484 13.7821645, -87.922049 13.7823086, -87.9219593 13.7822503, -87.9220588 13.7821061, -87.9221484 13.7821645))</t>
+          <t>POINT (-87.8182879 13.8097739)</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1121128779</t>
+          <t>https://www.openstreetmap.org/node/1642100520</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.78220737,-87.92205387</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8097739,-87.8182879</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hot-way-1121128779</t>
+          <t>hot-node-3968967150</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1640,12 +1655,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>way/1121128779</t>
+          <t>node/3968967150</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Unidad De Salud De Cantón Higueras</t>
+          <t>Sin nombre</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1660,12 +1675,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1675,7 +1690,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Lislique</t>
+          <t>Polorós</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1683,61 +1698,51 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>cantón Higueras</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Medicina general</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>13.78220737</t>
+          <t>13.8119375</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-87.92205387</t>
+          <t>-87.8167347</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>POLYGON ((-87.9220588 13.7821061, -87.9221484 13.7821645, -87.922049 13.7823086, -87.9219593 13.7822503, -87.9220588 13.7821061))</t>
+          <t>POINT (-87.8167347 13.8119375)</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1121128779</t>
+          <t>https://www.openstreetmap.org/node/3968967150</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.78220737,-87.92205387</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8119375,-87.8167347</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hot-way-286834891</t>
+          <t>hot-node-3971603602</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1747,32 +1752,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>way/286834891</t>
+          <t>node/3971603602</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hospital Nacional de La Unión</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1782,7 +1787,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Conchagua</t>
+          <t>El Sauce</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1790,56 +1795,51 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>La Unión</t>
-        </is>
-      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>13.347031</t>
+          <t>13.6668828</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-87.87606047</t>
+          <t>-87.7987511</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>POLYGON ((-87.8772038 13.3465709, -87.8753272 13.3460769, -87.8752685 13.3464042, -87.8750045 13.3475581, -87.8766924 13.34797, -87.876914 13.3473636, -87.8770837 13.3468996, -87.8772038 13.3465709))</t>
+          <t>POINT (-87.7987511 13.6668828)</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/286834891</t>
+          <t>https://www.openstreetmap.org/node/3971603602</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.347031,-87.87606047</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6668828,-87.7987511</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hot-node-3969572342</t>
+          <t>hot-node-3969559958</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1849,22 +1849,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>node/3969572342</t>
+          <t>node/3969559958</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Unidad de Salud Enfermera Ana María Alfaro de Sánchez</t>
+          <t>Unidad de Salud de Anamorós</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Puesto de salud</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>puesto_de_salud</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Nueva Esparta</t>
+          <t>Anamorós</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1892,6 +1892,16 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Anamorós</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>Point</t>
@@ -1904,12 +1914,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>13.7842859</t>
+          <t>13.7377762</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-87.8340675</t>
+          <t>-87.872437</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -1919,24 +1929,24 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>POINT (-87.8340675 13.7842859)</t>
+          <t>POINT (-87.872437 13.7377762)</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969572342</t>
+          <t>https://www.openstreetmap.org/node/3969559958</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7842859,-87.8340675</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7377762,-87.872437</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hot-node-1642100520</t>
+          <t>hot-node-3969545698</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1946,12 +1956,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>node/1642100520</t>
+          <t>node/3969545698</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sin nombre</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1981,7 +1991,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Polorós</t>
+          <t>Anamorós</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2001,12 +2011,12 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>13.8097739</t>
+          <t>13.741884</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-87.8182879</t>
+          <t>-87.8743634</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2016,24 +2026,24 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>POINT (-87.8182879 13.8097739)</t>
+          <t>POINT (-87.8743634 13.741884)</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1642100520</t>
+          <t>https://www.openstreetmap.org/node/3969545698</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8097739,-87.8182879</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.741884,-87.8743634</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hot-node-3968967150</t>
+          <t>hot-node-4129248327</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2043,22 +2053,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>node/3968967150</t>
+          <t>node/4129248327</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sin nombre</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2078,7 +2088,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Polorós</t>
+          <t>Meanguera del Golfo</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2086,6 +2096,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meanguera del Golfo</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2098,12 +2113,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>13.8119375</t>
+          <t>13.1773156</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-87.8167347</t>
+          <t>-87.696161</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2113,24 +2128,24 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>POINT (-87.8167347 13.8119375)</t>
+          <t>POINT (-87.696161 13.1773156)</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3968967150</t>
+          <t>https://www.openstreetmap.org/node/4129248327</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8119375,-87.8167347</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.1773156,-87.696161</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hot-node-3971603602</t>
+          <t>hot-node-4129248326</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2140,7 +2155,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>node/3971603602</t>
+          <t>node/4129248326</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2150,12 +2165,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2175,7 +2190,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>El Sauce</t>
+          <t>Meanguera del Golfo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2183,6 +2198,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meanguera del Golfo</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2195,12 +2215,12 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>13.6668828</t>
+          <t>13.1775224</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-87.7987511</t>
+          <t>-87.6960319</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2210,24 +2230,24 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>POINT (-87.7987511 13.6668828)</t>
+          <t>POINT (-87.6960319 13.1775224)</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3971603602</t>
+          <t>https://www.openstreetmap.org/node/4129248326</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6668828,-87.7987511</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.1775224,-87.6960319</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hot-node-3969559958</t>
+          <t>hot-node-3969243411</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2237,22 +2257,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>node/3969559958</t>
+          <t>node/3969243411</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Unidad de Salud de Anamorós</t>
+          <t>Cruz Roja Salvadoreña</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Puesto de salud</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>puesto_de_salud</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2272,7 +2292,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Anamorós</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2280,16 +2300,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Anamorós</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
       <c r="T19" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2302,12 +2312,12 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>13.7377762</t>
+          <t>13.3345734</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-87.872437</t>
+          <t>-87.8416114</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2317,24 +2327,24 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>POINT (-87.872437 13.7377762)</t>
+          <t>POINT (-87.8416114 13.3345734)</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969559958</t>
+          <t>https://www.openstreetmap.org/node/3969243411</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7377762,-87.872437</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3345734,-87.8416114</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hot-node-3969545698</t>
+          <t>hot-node-3969243408</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2344,12 +2354,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>node/3969545698</t>
+          <t>node/3969243408</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Clínica Medica Profamilia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2379,7 +2389,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Anamorós</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2399,12 +2409,12 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>13.741884</t>
+          <t>13.3363011</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-87.8743634</t>
+          <t>-87.841311</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2414,24 +2424,24 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>POINT (-87.8743634 13.741884)</t>
+          <t>POINT (-87.841311 13.3363011)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969545698</t>
+          <t>https://www.openstreetmap.org/node/3969243408</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.741884,-87.8743634</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3363011,-87.841311</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hot-node-4129248327</t>
+          <t>hot-node-3969266275</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2441,22 +2451,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>node/4129248327</t>
+          <t>node/3969266275</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Clínica Médica Familar</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2476,7 +2486,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Meanguera del Golfo</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2484,11 +2494,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Meanguera del Golfo</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2501,12 +2506,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>13.1773156</t>
+          <t>13.3369895</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-87.696161</t>
+          <t>-87.8396471</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2516,24 +2521,24 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>POINT (-87.696161 13.1773156)</t>
+          <t>POINT (-87.8396471 13.3369895)</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4129248327</t>
+          <t>https://www.openstreetmap.org/node/3969266275</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.1773156,-87.696161</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3369895,-87.8396471</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hot-node-4129248326</t>
+          <t>hot-node-3969266274</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2543,12 +2548,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>node/4129248326</t>
+          <t>node/3969266274</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Hospital Nacional</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2578,7 +2583,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Meanguera del Golfo</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2586,11 +2591,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Meanguera del Golfo</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>13.1775224</t>
+          <t>13.3374071</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-87.6960319</t>
+          <t>-87.8395559</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -2618,24 +2618,24 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>POINT (-87.6960319 13.1775224)</t>
+          <t>POINT (-87.8395559 13.3374071)</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4129248326</t>
+          <t>https://www.openstreetmap.org/node/3969266274</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.1775224,-87.6960319</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3374071,-87.8395559</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hot-node-3969243411</t>
+          <t>hot-node-3969266279</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>node/3969243411</t>
+          <t>node/3969266279</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cruz Roja Salvadoreña</t>
+          <t>Clínica Club de Leones</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>13.3345734</t>
+          <t>13.3377211</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-87.8416114</t>
+          <t>-87.8388502</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -2715,24 +2715,24 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>POINT (-87.8416114 13.3345734)</t>
+          <t>POINT (-87.8388502 13.3377211)</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969243411</t>
+          <t>https://www.openstreetmap.org/node/3969266279</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3345734,-87.8416114</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3377211,-87.8388502</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hot-node-3969243408</t>
+          <t>hot-node-4382639748</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2742,12 +2742,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>node/3969243408</t>
+          <t>node/4382639748</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Clínica Medica Profamilia</t>
+          <t>Clínica Medica San Jorge</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2785,6 +2785,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2797,12 +2802,12 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>13.3363011</t>
+          <t>13.3380019</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-87.841311</t>
+          <t>-87.8433012</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -2812,24 +2817,24 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>POINT (-87.841311 13.3363011)</t>
+          <t>POINT (-87.8433012 13.3380019)</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969243408</t>
+          <t>https://www.openstreetmap.org/node/4382639748</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3363011,-87.841311</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3380019,-87.8433012</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hot-node-3969266275</t>
+          <t>hot-node-2809112460</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2839,22 +2844,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>node/3969266275</t>
+          <t>node/2809112460</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Clínica Médica Familar</t>
+          <t>Clínica del ISSS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2894,12 +2899,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>13.3369895</t>
+          <t>13.3382435</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-87.8396471</t>
+          <t>-87.8426338</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -2909,24 +2914,24 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>POINT (-87.8396471 13.3369895)</t>
+          <t>POINT (-87.8426338 13.3382435)</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969266275</t>
+          <t>https://www.openstreetmap.org/node/2809112460</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3369895,-87.8396471</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3382435,-87.8426338</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hot-node-3969266274</t>
+          <t>hot-node-4381675651</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2936,22 +2941,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>node/3969266274</t>
+          <t>node/4381675651</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hospital Nacional</t>
+          <t>Unidad de Salud Cantón Huisquil</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2971,7 +2976,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Conchagua</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2991,12 +2996,12 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>13.3374071</t>
+          <t>13.3499923</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-87.8395559</t>
+          <t>-87.8593447</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3006,24 +3011,24 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>POINT (-87.8395559 13.3374071)</t>
+          <t>POINT (-87.8593447 13.3499923)</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969266274</t>
+          <t>https://www.openstreetmap.org/node/4381675651</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3374071,-87.8395559</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3499923,-87.8593447</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hot-node-3969266279</t>
+          <t>hot-node-6935977500</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3033,12 +3038,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>node/3969266279</t>
+          <t>node/6935977500</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Clínica Club de Leones</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3068,7 +3073,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Yucuaiquín</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3076,6 +3081,11 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Yucuaiquín</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3088,12 +3098,12 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>13.3377211</t>
+          <t>13.5502122</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-87.8388502</t>
+          <t>-88.0016585</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3103,24 +3113,24 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>POINT (-87.8388502 13.3377211)</t>
+          <t>POINT (-88.0016585 13.5502122)</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969266279</t>
+          <t>https://www.openstreetmap.org/node/6935977500</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3377211,-87.8388502</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5502122,-88.0016585</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hot-node-4382639748</t>
+          <t>hot-node-3969395280</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3130,12 +3140,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>node/4382639748</t>
+          <t>node/3969395280</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Clínica Medica San Jorge</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3165,7 +3175,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>San José</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3173,11 +3183,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>La Unión</t>
-        </is>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3190,12 +3195,12 @@
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>13.3380019</t>
+          <t>13.5617863</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-87.8433012</t>
+          <t>-87.9014804</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3205,24 +3210,24 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>POINT (-87.8433012 13.3380019)</t>
+          <t>POINT (-87.9014804 13.5617863)</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4382639748</t>
+          <t>https://www.openstreetmap.org/node/3969395280</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3380019,-87.8433012</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5617863,-87.9014804</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hot-node-2809112460</t>
+          <t>hot-node-3969348787</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3232,22 +3237,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>node/2809112460</t>
+          <t>node/3969348787</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Clínica del ISSS</t>
+          <t>Unidad de Salud</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3267,7 +3272,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3287,12 +3292,12 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>13.3382435</t>
+          <t>13.5730799</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-87.8426338</t>
+          <t>-87.9519753</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3302,24 +3307,24 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>POINT (-87.8426338 13.3382435)</t>
+          <t>POINT (-87.9519753 13.5730799)</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2809112460</t>
+          <t>https://www.openstreetmap.org/node/3969348787</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3382435,-87.8426338</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5730799,-87.9519753</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hot-node-4381675651</t>
+          <t>hot-node-3969495935</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3329,12 +3334,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>node/4381675651</t>
+          <t>node/3969495935</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Unidad de Salud Cantón Huisquil</t>
+          <t>Unidad de Salud de Pasaquina</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3364,7 +3369,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Conchagua</t>
+          <t>Pasaquina</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3384,12 +3389,12 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>13.3499923</t>
+          <t>13.5818405</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-87.8593447</t>
+          <t>-87.8367899</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -3399,24 +3404,24 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>POINT (-87.8593447 13.3499923)</t>
+          <t>POINT (-87.8367899 13.5818405)</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4381675651</t>
+          <t>https://www.openstreetmap.org/node/3969495935</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.3499923,-87.8593447</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5818405,-87.8367899</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hot-node-6935977500</t>
+          <t>hot-node-4775057927</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3426,22 +3431,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>node/6935977500</t>
+          <t>node/4775057927</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Hospital de Especialidades Santa Rosa de Lima</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3461,7 +3466,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Yucuaiquín</t>
+          <t>Santa Rosa de Lima</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3469,11 +3474,6 @@
           <t>Oriental</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Yucuaiquín</t>
-        </is>
-      </c>
       <c r="T31" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3486,12 +3486,12 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>13.5502122</t>
+          <t>13.6229267</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-88.0016585</t>
+          <t>-87.8940705</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -3501,24 +3501,24 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>POINT (-88.0016585 13.5502122)</t>
+          <t>POINT (-87.8940705 13.6229267)</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/6935977500</t>
+          <t>https://www.openstreetmap.org/node/4775057927</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5502122,-88.0016585</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6229267,-87.8940705</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hot-node-3969395280</t>
+          <t>hot-node-13520794421</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3528,22 +3528,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>node/3969395280</t>
+          <t>node/13520794421</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Unidad de Salud</t>
+          <t>Dr. Cristian Flores</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Consultorio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>consultorio</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>San José</t>
+          <t>Santa Rosa de Lima</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3571,6 +3571,16 @@
           <t>Oriental</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Lima</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Dermatología</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr">
         <is>
           <t>Point</t>
@@ -3583,12 +3593,12 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>13.5617863</t>
+          <t>13.6312873</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-87.9014804</t>
+          <t>-87.890524</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -3598,420 +3608,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>POINT (-87.9014804 13.5617863)</t>
+          <t>POINT (-87.890524 13.6312873)</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3969395280</t>
+          <t>https://www.openstreetmap.org/node/13520794421</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5617863,-87.9014804</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>hot-node-3969348787</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>node/3969348787</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Unidad de Salud</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>La Unión</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Bolívar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Oriental</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>13.5730799</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>-87.9519753</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>POINT (-87.9519753 13.5730799)</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/3969348787</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5730799,-87.9519753</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>hot-node-3969495935</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>node/3969495935</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Unidad de Salud de Pasaquina</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>La Unión</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Pasaquina</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Oriental</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>13.5818405</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>-87.8367899</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>POINT (-87.8367899 13.5818405)</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/3969495935</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.5818405,-87.8367899</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>hot-node-4775057927</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>node/4775057927</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Hospital de Especialidades Santa Rosa de Lima</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>La Unión</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Santa Rosa de Lima</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Oriental</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>13.6229267</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>-87.8940705</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>POINT (-87.8940705 13.6229267)</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/4775057927</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6229267,-87.8940705</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>hot-node-13520794421</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>node/13520794421</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Dr. Cristian Flores</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Consultorio</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>consultorio</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>La Unión</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Santa Rosa de Lima</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Oriental</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Santa Rosa de Lima</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Dermatología</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>13.6312873</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>-87.890524</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>POINT (-87.890524 13.6312873)</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/13520794421</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=13.6312873,-87.890524</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA36"/>
+  <autoFilter ref="A1:AA32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>